--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1012,13 +1012,10 @@
     <t>Person.telecom.system</t>
   </si>
   <si>
-    <t>phone | fax | email | pager | url | sms | other</t>
+    <t>« phone » pour Téléphone et Téléphone 2 ; « fax » pour Télécopie ; « email » pour adresse e-mail</t>
   </si>
   <si>
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
-  </si>
-  <si>
-    <t>« phone » pour Téléphone et Téléphone 2 ; « fax » pour Télécopie ; « email » pour adresse e-mail</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -6003,7 +6000,7 @@
         <v>320</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6032,28 +6029,28 @@
         <v>245</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Z39" t="s" s="2">
+      <c r="AA39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6062,27 +6059,27 @@
         <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6108,16 +6105,16 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -6166,7 +6163,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6181,21 +6178,21 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>335</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6221,16 +6218,16 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -6258,28 +6255,28 @@
         <v>245</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z41" t="s" s="2">
+      <c r="AA41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6300,15 +6297,15 @@
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6331,16 +6328,16 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6390,7 +6387,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6416,10 +6413,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6445,10 +6442,10 @@
         <v>293</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>296</v>
@@ -6501,7 +6498,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6527,10 +6524,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6556,16 +6553,16 @@
         <v>171</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6593,11 +6590,11 @@
         <v>245</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
       </c>
@@ -6614,7 +6611,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6629,21 +6626,21 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6666,19 +6663,19 @@
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6727,7 +6724,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6742,21 +6739,21 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6779,19 +6776,19 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6840,7 +6837,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6855,21 +6852,21 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>379</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6892,16 +6889,16 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6951,7 +6948,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6963,24 +6960,24 @@
         <v>98</v>
       </c>
       <c r="AJ47" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AK47" t="s" s="2">
+      <c r="AL47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7003,19 +7000,19 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7064,7 +7061,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7076,10 +7073,10 @@
         <v>98</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
@@ -7090,10 +7087,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7116,17 +7113,17 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7175,7 +7172,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7190,10 +7187,10 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>76</v>
@@ -7201,10 +7198,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7227,13 +7224,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7272,7 +7269,7 @@
         <v>76</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7282,7 +7279,7 @@
         <v>115</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7297,7 +7294,7 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7308,10 +7305,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7417,10 +7414,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7528,14 +7525,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7557,10 +7554,10 @@
         <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>112</v>
@@ -7615,7 +7612,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7641,10 +7638,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7667,16 +7664,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7726,7 +7723,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>86</v>
@@ -7738,10 +7735,10 @@
         <v>98</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7752,10 +7749,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7781,10 +7778,10 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>278</v>
@@ -7816,11 +7813,11 @@
         <v>245</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>76</v>
       </c>
@@ -7837,7 +7834,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7852,7 +7849,7 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7863,13 +7860,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>76</v>
@@ -7891,13 +7888,13 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7948,7 +7945,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7963,7 +7960,7 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7974,10 +7971,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8083,10 +8080,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8194,14 +8191,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8223,10 +8220,10 @@
         <v>109</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>112</v>
@@ -8281,7 +8278,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8307,10 +8304,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8333,16 +8330,16 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8392,7 +8389,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8404,10 +8401,10 @@
         <v>98</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8418,10 +8415,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8447,10 +8444,10 @@
         <v>171</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>278</v>
@@ -8482,11 +8479,11 @@
         <v>245</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>76</v>
       </c>
@@ -8503,7 +8500,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8518,7 +8515,7 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:09:13+00:00</t>
+    <t>2024-02-05T18:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-person.xlsx
+++ b/ig/main/StructureDefinition-as-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
